--- a/templates/TATA Capital/TATA_Collection_and_Repo_Agency_Template_2026-27.xlsx
+++ b/templates/TATA Capital/TATA_Collection_and_Repo_Agency_Template_2026-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-automation-final\templates\TATA Capital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C68EAD-17AD-4A05-A259-EB63F503E470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71550EC1-1BDA-448A-9C1A-6A1B666ADD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="13152" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="2" r:id="rId1"/>
@@ -3330,6 +3330,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B89E9B38EF334341B754D8F8D6A719DA" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fa1e129258e112aee4cf2e89d18a6563">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xmlns:ns4="2bc29a05-2ca3-4765-9547-41c11361a102" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5debfbfacc377353d2d2775bb411679" ns3:_="" ns4:_="">
     <xsd:import namespace="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
@@ -3568,24 +3585,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8B9EEC0-8330-40FD-B3DF-37C58251D9C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2570D5D0-D08A-4BFE-8542-1AE4D1BDE57D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
+    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDED7350-1E0A-47E5-88B4-E30F305BEE64}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3602,29 +3627,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8B9EEC0-8330-40FD-B3DF-37C58251D9C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2570D5D0-D08A-4BFE-8542-1AE4D1BDE57D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
-    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>